--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountEndSub.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdAccountEndSub.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92375C2F-AAEA-4E9F-9D5E-E92BB789F0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="资产池终止信息" sheetId="5" r:id="rId1"/>
@@ -15,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>数据状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,11 +51,14 @@
     <t>反馈资产池代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>内部产品代码</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -150,7 +154,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -214,7 +218,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,9 +251,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -282,6 +303,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -457,19 +495,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="4"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="4"/>
-    <col min="7" max="7" width="13.375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" style="4" customWidth="1"/>
+    <col min="9" max="10" width="17.21875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -495,6 +533,9 @@
         <v>8</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -506,549 +547,549 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179"/>
     </row>
   </sheetData>
